--- a/data/annotation/ПРОВЕРКА_разметки_новостей.xlsx
+++ b/data/annotation/ПРОВЕРКА_разметки_новостей.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="140" customWidth="1" min="1" max="1"/>
@@ -463,12 +463,19 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Спорные случаи отмечены в комментарии — их стоит посмотреть внимательнее.</t>
+          <t>Масштаб и длительность: «да» ставим, только если событие затрагивает больше ~100 человек и длится дольше нескольких дней. Локальные и короткие события (перекрытие дороги или остановка транспорта на день-два, пожар в посёлке, обрушение одного дома, авария с цистерной) — «нет»: на траты за целый месяц они не влияют. При дневных данных о продажах такие события могли бы пригодиться для прогноза на дни вперёд.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
+        <is>
+          <t>Спорные случаи отмечены в комментарии — их стоит посмотреть внимательнее.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>После проверки поставьте «+» в последней колонке и сохраните файл. Пересчёт: python -m src.news.annotation score</t>
         </is>
@@ -546,8 +553,6 @@
           <t>да</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -570,8 +575,6 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -594,8 +597,6 @@
           <t>да</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -618,8 +619,6 @@
           <t>да</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -642,8 +641,6 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -666,8 +663,6 @@
           <t>да</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -690,8 +685,6 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -714,8 +707,6 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -738,8 +729,6 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -762,8 +751,6 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -786,8 +773,6 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -810,8 +795,6 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -834,8 +817,6 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -855,15 +836,14 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>спорно: пожары в посёлках — масштаб неясен</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr"/>
+          <t>нет: локальное или короткое событие (меньше 100 человек или на день-два), на месячные траты не влияет</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -886,8 +866,6 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -910,8 +888,6 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -934,8 +910,6 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -958,8 +932,6 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -982,8 +954,6 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1006,8 +976,6 @@
           <t>да</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1030,8 +998,6 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1054,8 +1020,6 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1078,8 +1042,6 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1102,8 +1064,6 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1126,8 +1086,6 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1150,8 +1108,6 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1174,8 +1130,6 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1198,8 +1152,6 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1222,8 +1174,6 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1246,8 +1196,6 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1267,15 +1215,14 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>спорно: подтопление ограничило движение — масштаб неясен</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr"/>
+          <t>нет: локальное или короткое событие (меньше 100 человек или на день-два), на месячные траты не влияет</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1298,8 +1245,6 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1322,8 +1267,6 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1346,8 +1289,6 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1370,8 +1311,6 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1394,8 +1333,6 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1418,8 +1355,6 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1442,8 +1377,6 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1471,7 +1404,6 @@
           <t>спорно: сильный снегопад — погода, не ЧС</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1494,8 +1426,6 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1518,8 +1448,6 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1542,8 +1470,6 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1566,8 +1492,6 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1590,8 +1514,6 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1616,10 +1538,9 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>спорно: визит министра, но в зону идущего паводка</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr"/>
+          <t>да: визит министра, но в зону идущего паводка</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1642,8 +1563,6 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1666,8 +1585,6 @@
           <t>да</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr"/>
-      <c r="F48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1690,8 +1607,6 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1714,8 +1629,6 @@
           <t>да</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr"/>
-      <c r="F50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1738,8 +1651,6 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1762,8 +1673,6 @@
           <t>да</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1786,8 +1695,6 @@
           <t>да</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1810,8 +1717,6 @@
           <t>да</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1839,7 +1744,6 @@
           <t>спорно: эвакуация детского лагеря — мелко</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1862,8 +1766,6 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr"/>
-      <c r="F56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1888,10 +1790,9 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>спорно: о готовности, но во время паводка</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr"/>
+          <t>да: о готовности, но во время паводка</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1914,8 +1815,6 @@
           <t>да</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr"/>
-      <c r="F58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -1938,8 +1837,6 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr"/>
-      <c r="F59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -1962,8 +1859,6 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr"/>
-      <c r="F60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -1986,8 +1881,6 @@
           <t>да</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr"/>
-      <c r="F61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2010,8 +1903,6 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr"/>
-      <c r="F62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2034,8 +1925,6 @@
           <t>да</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr"/>
-      <c r="F63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2058,8 +1947,6 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr"/>
-      <c r="F64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2082,8 +1969,6 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr"/>
-      <c r="F65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2106,8 +1991,6 @@
           <t>да</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr"/>
-      <c r="F66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2130,8 +2013,6 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr"/>
-      <c r="F67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2154,8 +2035,6 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr"/>
-      <c r="F68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2180,10 +2059,9 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>спорно: заседание комиссии, но по идущему паводку</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr"/>
+          <t>да: заседание комиссии, но по идущему паводку</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2206,8 +2084,6 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr"/>
-      <c r="F70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2230,8 +2106,6 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr"/>
-      <c r="F71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2254,8 +2128,6 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr"/>
-      <c r="F72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2278,8 +2150,6 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr"/>
-      <c r="F73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2302,8 +2172,6 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr"/>
-      <c r="F74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2328,10 +2196,9 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>спорно: эвакуация детей из-за обстрелов — массовая</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr"/>
+          <t>да: эвакуация детей из-за обстрелов — массовая</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2354,8 +2221,6 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr"/>
-      <c r="F76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2378,8 +2243,6 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr"/>
-      <c r="F77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2402,8 +2265,6 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr"/>
-      <c r="F78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2426,8 +2287,6 @@
           <t>да</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr"/>
-      <c r="F79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2450,8 +2309,6 @@
           <t>да</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr"/>
-      <c r="F80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -2474,8 +2331,6 @@
           <t>да</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr"/>
-      <c r="F81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -2498,8 +2353,6 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr"/>
-      <c r="F82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -2522,8 +2375,6 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr"/>
-      <c r="F83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -2546,8 +2397,6 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr"/>
-      <c r="F84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -2570,8 +2419,6 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr"/>
-      <c r="F85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -2594,8 +2441,6 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr"/>
-      <c r="F86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -2618,8 +2463,6 @@
           <t>да</t>
         </is>
       </c>
-      <c r="E87" t="inlineStr"/>
-      <c r="F87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -2642,8 +2485,6 @@
           <t>да</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr"/>
-      <c r="F88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -2666,8 +2507,6 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr"/>
-      <c r="F89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -2690,8 +2529,6 @@
           <t>да</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr"/>
-      <c r="F90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -2714,8 +2551,6 @@
           <t>да</t>
         </is>
       </c>
-      <c r="E91" t="inlineStr"/>
-      <c r="F91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -2738,8 +2573,6 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="E92" t="inlineStr"/>
-      <c r="F92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -2767,7 +2600,6 @@
           <t>спорно: крушение поезда — крупная авария, но не территория</t>
         </is>
       </c>
-      <c r="F93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -2790,8 +2622,6 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="E94" t="inlineStr"/>
-      <c r="F94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -2814,8 +2644,6 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="E95" t="inlineStr"/>
-      <c r="F95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -2838,8 +2666,6 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="E96" t="inlineStr"/>
-      <c r="F96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -2862,8 +2688,6 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="E97" t="inlineStr"/>
-      <c r="F97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -2886,8 +2710,6 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="E98" t="inlineStr"/>
-      <c r="F98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -2915,7 +2737,6 @@
           <t>спорно: «обстановка сложная» — без конкретики</t>
         </is>
       </c>
-      <c r="F99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -2938,8 +2759,6 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="E100" t="inlineStr"/>
-      <c r="F100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -2962,8 +2781,6 @@
           <t>да</t>
         </is>
       </c>
-      <c r="E101" t="inlineStr"/>
-      <c r="F101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -2991,7 +2808,6 @@
           <t>спорно: эвакуация одного дома</t>
         </is>
       </c>
-      <c r="F102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -3014,8 +2830,6 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="E103" t="inlineStr"/>
-      <c r="F103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -3038,8 +2852,6 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="E104" t="inlineStr"/>
-      <c r="F104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -3062,8 +2874,6 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="E105" t="inlineStr"/>
-      <c r="F105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -3086,8 +2896,6 @@
           <t>да</t>
         </is>
       </c>
-      <c r="E106" t="inlineStr"/>
-      <c r="F106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -3110,8 +2918,6 @@
           <t>да</t>
         </is>
       </c>
-      <c r="E107" t="inlineStr"/>
-      <c r="F107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -3131,15 +2937,14 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>спорно: режим ЧС, но из-за обрушения одного дома</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr"/>
+          <t>нет: локальное или короткое событие (меньше 100 человек или на день-два), на месячные траты не влияет</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -3167,7 +2972,6 @@
           <t>спорно: землетрясение 6,0 без сообщений о разрушениях</t>
         </is>
       </c>
-      <c r="F109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -3190,8 +2994,6 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="E110" t="inlineStr"/>
-      <c r="F110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -3214,8 +3016,6 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="E111" t="inlineStr"/>
-      <c r="F111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -3238,8 +3038,6 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="E112" t="inlineStr"/>
-      <c r="F112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -3262,8 +3060,6 @@
           <t>да</t>
         </is>
       </c>
-      <c r="E113" t="inlineStr"/>
-      <c r="F113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -3286,8 +3082,6 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="E114" t="inlineStr"/>
-      <c r="F114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -3310,8 +3104,6 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="E115" t="inlineStr"/>
-      <c r="F115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -3339,7 +3131,6 @@
           <t>спорно: отставка мэра после наводнения — о политике</t>
         </is>
       </c>
-      <c r="F116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -3362,8 +3153,6 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="E117" t="inlineStr"/>
-      <c r="F117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -3386,8 +3175,6 @@
           <t>да</t>
         </is>
       </c>
-      <c r="E118" t="inlineStr"/>
-      <c r="F118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -3410,8 +3197,6 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="E119" t="inlineStr"/>
-      <c r="F119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -3434,8 +3219,6 @@
           <t>да</t>
         </is>
       </c>
-      <c r="E120" t="inlineStr"/>
-      <c r="F120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -3458,8 +3241,6 @@
           <t>да</t>
         </is>
       </c>
-      <c r="E121" t="inlineStr"/>
-      <c r="F121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -3482,8 +3263,6 @@
           <t>да</t>
         </is>
       </c>
-      <c r="E122" t="inlineStr"/>
-      <c r="F122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -3503,15 +3282,14 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>спорно: режим ЧС после аварии танкеров — локально</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr"/>
+          <t>нет: локальное или короткое событие (меньше 100 человек или на день-два), на месячные траты не влияет</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -3534,8 +3312,6 @@
           <t>да</t>
         </is>
       </c>
-      <c r="E124" t="inlineStr"/>
-      <c r="F124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -3558,8 +3334,6 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="E125" t="inlineStr"/>
-      <c r="F125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -3582,8 +3356,6 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="E126" t="inlineStr"/>
-      <c r="F126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -3606,8 +3378,6 @@
           <t>да</t>
         </is>
       </c>
-      <c r="E127" t="inlineStr"/>
-      <c r="F127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -3630,8 +3400,6 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="E128" t="inlineStr"/>
-      <c r="F128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -3654,8 +3422,6 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="E129" t="inlineStr"/>
-      <c r="F129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -3683,7 +3449,6 @@
           <t>спорно: тушение ландшафтных пожаров — масштаб неясен</t>
         </is>
       </c>
-      <c r="F130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -3706,8 +3471,6 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="E131" t="inlineStr"/>
-      <c r="F131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -3730,8 +3493,6 @@
           <t>да</t>
         </is>
       </c>
-      <c r="E132" t="inlineStr"/>
-      <c r="F132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -3754,8 +3515,6 @@
           <t>да</t>
         </is>
       </c>
-      <c r="E133" t="inlineStr"/>
-      <c r="F133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -3775,15 +3534,14 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>спорно: эвакуация сёл из-за пожара на полигоне</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr"/>
+          <t>нет: локальное или короткое событие (меньше 100 человек или на день-два), на месячные траты не влияет</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -3806,8 +3564,6 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="E135" t="inlineStr"/>
-      <c r="F135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -3830,8 +3586,6 @@
           <t>да</t>
         </is>
       </c>
-      <c r="E136" t="inlineStr"/>
-      <c r="F136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -3854,8 +3608,6 @@
           <t>да</t>
         </is>
       </c>
-      <c r="E137" t="inlineStr"/>
-      <c r="F137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -3878,8 +3630,6 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="E138" t="inlineStr"/>
-      <c r="F138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -3902,8 +3652,6 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="E139" t="inlineStr"/>
-      <c r="F139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -3926,8 +3674,6 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="E140" t="inlineStr"/>
-      <c r="F140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -3950,8 +3696,6 @@
           <t>да</t>
         </is>
       </c>
-      <c r="E141" t="inlineStr"/>
-      <c r="F141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -3974,8 +3718,6 @@
           <t>да</t>
         </is>
       </c>
-      <c r="E142" t="inlineStr"/>
-      <c r="F142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -3998,8 +3740,6 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="E143" t="inlineStr"/>
-      <c r="F143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -4022,8 +3762,6 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="E144" t="inlineStr"/>
-      <c r="F144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -4046,8 +3784,6 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="E145" t="inlineStr"/>
-      <c r="F145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -4070,8 +3806,6 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="E146" t="inlineStr"/>
-      <c r="F146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -4094,8 +3828,6 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="E147" t="inlineStr"/>
-      <c r="F147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -4118,8 +3850,6 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="E148" t="inlineStr"/>
-      <c r="F148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -4142,8 +3872,6 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="E149" t="inlineStr"/>
-      <c r="F149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -4166,8 +3894,6 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="E150" t="inlineStr"/>
-      <c r="F150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -4190,8 +3916,6 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="E151" t="inlineStr"/>
-      <c r="F151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -4214,8 +3938,6 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="E152" t="inlineStr"/>
-      <c r="F152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -4238,8 +3960,6 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="E153" t="inlineStr"/>
-      <c r="F153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -4259,15 +3979,14 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>спорно: режим ЧС из-за цистерны с аммиаком — локально</t>
-        </is>
-      </c>
-      <c r="F154" t="inlineStr"/>
+          <t>нет: локальное или короткое событие (меньше 100 человек или на день-два), на месячные траты не влияет</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -4290,8 +4009,6 @@
           <t>да</t>
         </is>
       </c>
-      <c r="E155" t="inlineStr"/>
-      <c r="F155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -4314,8 +4031,6 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="E156" t="inlineStr"/>
-      <c r="F156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -4338,8 +4053,6 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="E157" t="inlineStr"/>
-      <c r="F157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -4362,8 +4075,6 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="E158" t="inlineStr"/>
-      <c r="F158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -4386,8 +4097,6 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="E159" t="inlineStr"/>
-      <c r="F159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -4410,8 +4119,6 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="E160" t="inlineStr"/>
-      <c r="F160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -4434,8 +4141,6 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="E161" t="inlineStr"/>
-      <c r="F161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -4458,8 +4163,6 @@
           <t>да</t>
         </is>
       </c>
-      <c r="E162" t="inlineStr"/>
-      <c r="F162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -4482,8 +4185,6 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="E163" t="inlineStr"/>
-      <c r="F163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -4506,8 +4207,6 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="E164" t="inlineStr"/>
-      <c r="F164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -4530,8 +4229,6 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="E165" t="inlineStr"/>
-      <c r="F165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -4554,8 +4251,6 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="E166" t="inlineStr"/>
-      <c r="F166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -4578,8 +4273,6 @@
           <t>да</t>
         </is>
       </c>
-      <c r="E167" t="inlineStr"/>
-      <c r="F167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -4602,8 +4295,6 @@
           <t>да</t>
         </is>
       </c>
-      <c r="E168" t="inlineStr"/>
-      <c r="F168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -4626,8 +4317,6 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="E169" t="inlineStr"/>
-      <c r="F169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -4650,8 +4339,6 @@
           <t>да</t>
         </is>
       </c>
-      <c r="E170" t="inlineStr"/>
-      <c r="F170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -4674,8 +4361,6 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="E171" t="inlineStr"/>
-      <c r="F171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -4698,8 +4383,6 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="E172" t="inlineStr"/>
-      <c r="F172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -4722,8 +4405,6 @@
           <t>да</t>
         </is>
       </c>
-      <c r="E173" t="inlineStr"/>
-      <c r="F173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -4746,8 +4427,6 @@
           <t>да</t>
         </is>
       </c>
-      <c r="E174" t="inlineStr"/>
-      <c r="F174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -4770,8 +4449,6 @@
           <t>да</t>
         </is>
       </c>
-      <c r="E175" t="inlineStr"/>
-      <c r="F175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -4794,8 +4471,6 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="E176" t="inlineStr"/>
-      <c r="F176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -4815,15 +4490,14 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>спорно: режим ЧС из-за снегопада в одном городе</t>
-        </is>
-      </c>
-      <c r="F177" t="inlineStr"/>
+          <t>нет: локальное или короткое событие (меньше 100 человек или на день-два), на месячные траты не влияет</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -4846,8 +4520,6 @@
           <t>да</t>
         </is>
       </c>
-      <c r="E178" t="inlineStr"/>
-      <c r="F178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -4870,8 +4542,6 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="E179" t="inlineStr"/>
-      <c r="F179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -4896,10 +4566,9 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>спорно: режим ЧС из-за засухи — влияет на аграриев</t>
-        </is>
-      </c>
-      <c r="F180" t="inlineStr"/>
+          <t>да: режим ЧС из-за засухи — влияет на аграриев</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -4922,8 +4591,6 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="E181" t="inlineStr"/>
-      <c r="F181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -4946,8 +4613,6 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="E182" t="inlineStr"/>
-      <c r="F182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -4970,8 +4635,6 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="E183" t="inlineStr"/>
-      <c r="F183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -4994,8 +4657,6 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="E184" t="inlineStr"/>
-      <c r="F184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -5018,8 +4679,6 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="E185" t="inlineStr"/>
-      <c r="F185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -5042,8 +4701,6 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="E186" t="inlineStr"/>
-      <c r="F186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -5066,8 +4723,6 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="E187" t="inlineStr"/>
-      <c r="F187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -5090,8 +4745,6 @@
           <t>да</t>
         </is>
       </c>
-      <c r="E188" t="inlineStr"/>
-      <c r="F188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -5114,8 +4767,6 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="E189" t="inlineStr"/>
-      <c r="F189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -5135,15 +4786,14 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>спорно: авария на ТЭЦ: отключение тепла в городе</t>
-        </is>
-      </c>
-      <c r="F190" t="inlineStr"/>
+          <t>нет: локальное или короткое событие (меньше 100 человек или на день-два), на месячные траты не влияет</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -5166,8 +4816,6 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="E191" t="inlineStr"/>
-      <c r="F191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -5190,8 +4838,6 @@
           <t>да</t>
         </is>
       </c>
-      <c r="E192" t="inlineStr"/>
-      <c r="F192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -5214,8 +4860,6 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="E193" t="inlineStr"/>
-      <c r="F193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -5238,8 +4882,6 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="E194" t="inlineStr"/>
-      <c r="F194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -5262,8 +4904,6 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="E195" t="inlineStr"/>
-      <c r="F195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -5286,8 +4926,6 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="E196" t="inlineStr"/>
-      <c r="F196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -5310,8 +4948,6 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="E197" t="inlineStr"/>
-      <c r="F197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -5334,8 +4970,6 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="E198" t="inlineStr"/>
-      <c r="F198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -5358,8 +4992,6 @@
           <t>да</t>
         </is>
       </c>
-      <c r="E199" t="inlineStr"/>
-      <c r="F199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -5382,8 +5014,6 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="E200" t="inlineStr"/>
-      <c r="F200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -5406,8 +5036,6 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="E201" t="inlineStr"/>
-      <c r="F201" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
